--- a/conformance/fixtures/087-date-canonical-string-concat/data.xlsx
+++ b/conformance/fixtures/087-date-canonical-string-concat/data.xlsx
@@ -421,7 +421,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>46149.625</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -429,7 +429,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>46150.02083333333</v>
+        <v>46150.39583333333</v>
       </c>
     </row>
   </sheetData>
